--- a/results/BECCS_scenarios_summary.xlsx
+++ b/results/BECCS_scenarios_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,20 +441,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>T_max_Mt_yr</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>biomass_transport</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>co2_transport</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>water_transport</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>transport_cost_bnUSD_yr</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>unit_cost_USD_per_tCO2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -470,7 +485,7 @@
         <v>197.934651517</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>197.9346522268447</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -478,7 +493,16 @@
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
@@ -491,18 +515,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>606.2368703879999</v>
+        <v>606.236851388</v>
       </c>
       <c r="C3" t="n">
-        <v>408.302218312</v>
+        <v>606.2368509823394</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>408.302199561</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>16.16049807336793</v>
+      </c>
+      <c r="H3" t="n">
+        <v>26.65706981746148</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
@@ -515,18 +548,27 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>591.3602702900002</v>
+        <v>591.3602405900003</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>591.3602406727011</v>
       </c>
       <c r="D4" t="n">
-        <v>393.5857453850001</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
+        <v>393.4255886750001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4.242816528128561</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7.174673298792461</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
@@ -539,18 +581,27 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1145.976391824</v>
+        <v>1145.976392764</v>
       </c>
       <c r="C5" t="n">
-        <v>559.6268029814001</v>
+        <v>1145.976391269818</v>
       </c>
       <c r="D5" t="n">
-        <v>755.3787083539999</v>
+        <v>554.6161212430001</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr">
+        <v>728.8943677479999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20.72380850794215</v>
+      </c>
+      <c r="H5" t="n">
+        <v>18.08397506161366</v>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
@@ -563,18 +614,27 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1145.976391824</v>
+        <v>1145.976391018999</v>
       </c>
       <c r="C6" t="n">
-        <v>556.4584492014001</v>
+        <v>1145.976391269818</v>
       </c>
       <c r="D6" t="n">
-        <v>755.3787083539999</v>
+        <v>131.023030752</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr">
+        <v>658.830935478</v>
+      </c>
+      <c r="F6" t="n">
+        <v>464.6933665400001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9.392829854231922</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8.196355464077092</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
